--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1661,6 +1661,115 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131905065</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92272</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 12198, Mosjön, Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>565247</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6429713</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131886682</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131886754</v>
       </c>
       <c r="B3" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131886976</v>
       </c>
       <c r="B4" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131886960</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131886916</v>
+        <v>131886896</v>
       </c>
       <c r="B6" t="n">
-        <v>106160</v>
+        <v>91211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,31 +1121,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565113</v>
+        <v>565232</v>
       </c>
       <c r="R6" t="n">
-        <v>6429840</v>
+        <v>6429687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1192,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,7 +1227,7 @@
         <v>131886806</v>
       </c>
       <c r="B7" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131886896</v>
+        <v>131886916</v>
       </c>
       <c r="B8" t="n">
-        <v>91205</v>
+        <v>106166</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,34 +1349,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565232</v>
+        <v>565113</v>
       </c>
       <c r="R8" t="n">
-        <v>6429687</v>
+        <v>6429840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,11 +1417,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1447,7 @@
         <v>131886716</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131886873</v>
       </c>
       <c r="B10" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>131905065</v>
       </c>
       <c r="B11" t="n">
-        <v>92272</v>
+        <v>92277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131886682</v>
       </c>
       <c r="B2" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131886976</v>
       </c>
       <c r="B4" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131886960</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131886806</v>
+        <v>131886896</v>
       </c>
       <c r="B6" t="n">
-        <v>58107</v>
+        <v>91265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,13 +1143,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565244</v>
+        <v>565232</v>
       </c>
       <c r="R6" t="n">
-        <v>6429749</v>
+        <v>6429687</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1196,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
+          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,6 +1205,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,42 +1224,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131886916</v>
+        <v>131886806</v>
       </c>
       <c r="B7" t="n">
-        <v>106219</v>
+        <v>58109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565113</v>
+        <v>565244</v>
       </c>
       <c r="R7" t="n">
-        <v>6429840</v>
+        <v>6429749</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,13 +1309,17 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131886896</v>
+        <v>131886916</v>
       </c>
       <c r="B8" t="n">
-        <v>91262</v>
+        <v>106222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,34 +1349,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565232</v>
+        <v>565113</v>
       </c>
       <c r="R8" t="n">
-        <v>6429687</v>
+        <v>6429840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,11 +1417,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,7 +1557,7 @@
         <v>131886873</v>
       </c>
       <c r="B10" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>131905065</v>
       </c>
       <c r="B11" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -1110,32 +1110,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131886896</v>
+        <v>131886806</v>
       </c>
       <c r="B6" t="n">
-        <v>91265</v>
+        <v>58109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,12 +1143,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565232</v>
+        <v>565244</v>
       </c>
       <c r="R6" t="n">
-        <v>6429687</v>
+        <v>6429749</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallåga i soligt läge</t>
+          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1206,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,32 +1224,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131886806</v>
+        <v>131886896</v>
       </c>
       <c r="B7" t="n">
-        <v>58109</v>
+        <v>91265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,13 +1257,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565244</v>
+        <v>565232</v>
       </c>
       <c r="R7" t="n">
-        <v>6429749</v>
+        <v>6429687</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,7 +1310,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
+          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,6 +1319,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -1110,32 +1110,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131886806</v>
+        <v>131886896</v>
       </c>
       <c r="B6" t="n">
-        <v>58109</v>
+        <v>91265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,13 +1143,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565244</v>
+        <v>565232</v>
       </c>
       <c r="R6" t="n">
-        <v>6429749</v>
+        <v>6429687</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1196,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
+          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,6 +1205,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,32 +1224,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131886896</v>
+        <v>131886806</v>
       </c>
       <c r="B7" t="n">
-        <v>91265</v>
+        <v>58109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,12 +1257,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565232</v>
+        <v>565244</v>
       </c>
       <c r="R7" t="n">
-        <v>6429687</v>
+        <v>6429749</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1311,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På tallåga i soligt läge</t>
+          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1320,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131886682</v>
       </c>
       <c r="B2" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>131886754</v>
       </c>
       <c r="B3" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131886976</v>
       </c>
       <c r="B4" t="n">
-        <v>106222</v>
+        <v>106230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131886960</v>
       </c>
       <c r="B5" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,32 +1110,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131886896</v>
+        <v>131886806</v>
       </c>
       <c r="B6" t="n">
-        <v>91265</v>
+        <v>58110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,12 +1143,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565232</v>
+        <v>565244</v>
       </c>
       <c r="R6" t="n">
-        <v>6429687</v>
+        <v>6429749</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tallåga i soligt läge</t>
+          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1206,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,46 +1224,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131886806</v>
+        <v>131886916</v>
       </c>
       <c r="B7" t="n">
-        <v>58109</v>
+        <v>106230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565244</v>
+        <v>565113</v>
       </c>
       <c r="R7" t="n">
-        <v>6429749</v>
+        <v>6429840</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,17 +1305,13 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131886916</v>
+        <v>131886896</v>
       </c>
       <c r="B8" t="n">
-        <v>106222</v>
+        <v>91271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,31 +1341,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565113</v>
+        <v>565232</v>
       </c>
       <c r="R8" t="n">
-        <v>6429840</v>
+        <v>6429687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,6 +1412,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1447,7 @@
         <v>131886716</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>131886873</v>
       </c>
       <c r="B10" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>131905065</v>
       </c>
       <c r="B11" t="n">
-        <v>92331</v>
+        <v>92337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131886682</v>
+        <v>131886944</v>
       </c>
       <c r="B2" t="n">
-        <v>58110</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565449</v>
+        <v>565145</v>
       </c>
       <c r="R2" t="n">
-        <v>6430186</v>
+        <v>6429836</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Även sång</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131886754</v>
+        <v>131905065</v>
       </c>
       <c r="B3" t="n">
-        <v>57137</v>
+        <v>92385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,31 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565225</v>
+        <v>565247</v>
       </c>
       <c r="R3" t="n">
-        <v>6429789</v>
+        <v>6429713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,42 +898,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131886976</v>
+        <v>131886873</v>
       </c>
       <c r="B4" t="n">
-        <v>106230</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565057</v>
+        <v>565258</v>
       </c>
       <c r="R4" t="n">
-        <v>6429932</v>
+        <v>6429747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,46 +1007,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131886960</v>
+        <v>131886896</v>
       </c>
       <c r="B5" t="n">
-        <v>99106</v>
+        <v>91347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565080</v>
+        <v>565232</v>
       </c>
       <c r="R5" t="n">
-        <v>6429903</v>
+        <v>6429687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1089,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,44 +1121,40 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131886806</v>
+        <v>131886716</v>
       </c>
       <c r="B6" t="n">
-        <v>58110</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1157,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565244</v>
+        <v>565417</v>
       </c>
       <c r="R6" t="n">
-        <v>6429749</v>
+        <v>6430139</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1204,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131886916</v>
+        <v>131886754</v>
       </c>
       <c r="B7" t="n">
-        <v>106230</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,31 +1242,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565113</v>
+        <v>565225</v>
       </c>
       <c r="R7" t="n">
-        <v>6429840</v>
+        <v>6429789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1318,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131886896</v>
+        <v>131886682</v>
       </c>
       <c r="B8" t="n">
-        <v>91271</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,12 +1369,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,13 +1383,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565232</v>
+        <v>565449</v>
       </c>
       <c r="R8" t="n">
-        <v>6429687</v>
+        <v>6430186</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1423,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tallåga i soligt läge</t>
+          <t>Även sång</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1432,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1444,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131886716</v>
+        <v>131886806</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,29 +1461,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1487,13 +1497,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565417</v>
+        <v>565244</v>
       </c>
       <c r="R9" t="n">
-        <v>6430139</v>
+        <v>6429749</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1537,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,45 +1564,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131886873</v>
+        <v>131886960</v>
       </c>
       <c r="B10" t="n">
-        <v>91919</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565258</v>
+        <v>565080</v>
       </c>
       <c r="R10" t="n">
-        <v>6429747</v>
+        <v>6429903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131905065</v>
+        <v>131886916</v>
       </c>
       <c r="B11" t="n">
-        <v>92337</v>
+        <v>106324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,34 +1685,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1709,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565247</v>
+        <v>565113</v>
       </c>
       <c r="R11" t="n">
-        <v>6429713</v>
+        <v>6429840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,6 +1777,112 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131886976</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 12198, Mosjön, Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>565057</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6429932</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12198-2026 artfynd.xlsx
+++ b/artfynd/A 12198-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,45 +799,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131905065</v>
+        <v>131886960</v>
       </c>
       <c r="B3" t="n">
-        <v>92385</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565247</v>
+        <v>565080</v>
       </c>
       <c r="R3" t="n">
-        <v>6429713</v>
+        <v>6429903</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,51 +908,48 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131905065</t>
+          <t>https://artportalen.se/Sighting/131886960</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131886873</v>
+        <v>131886916</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>106324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565258</v>
+        <v>565113</v>
       </c>
       <c r="R4" t="n">
-        <v>6429747</v>
+        <v>6429840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,16 +1019,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131886873</t>
+          <t>https://artportalen.se/Sighting/131886916</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131886896</v>
+        <v>131886976</v>
       </c>
       <c r="B5" t="n">
-        <v>91347</v>
+        <v>106324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,34 +1036,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5685</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565232</v>
+        <v>565057</v>
       </c>
       <c r="R5" t="n">
-        <v>6429687</v>
+        <v>6429932</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,11 +1104,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallåga i soligt läge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,806 +1129,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886896</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>131886716</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>565417</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6430139</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886716</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>131886754</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57162</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>565225</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6429789</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886754</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>131886682</v>
-      </c>
-      <c r="B8" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>565449</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6430186</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886682</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>131886806</v>
-      </c>
-      <c r="B9" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>565244</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6429749</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hördes samtidigt som den längre norrut! 2 revir!</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886806</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>131886960</v>
-      </c>
-      <c r="B10" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>565080</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6429903</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886960</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>131886916</v>
-      </c>
-      <c r="B11" t="n">
-        <v>106324</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>565113</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6429840</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/131886916</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>131886976</v>
-      </c>
-      <c r="B12" t="n">
-        <v>106324</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>A 12198, Mosjön, Tyllinge, Sm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>565057</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6429932</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Dalhem</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131886976</t>
         </is>
@@ -1950,13 +1140,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
